--- a/dev/ValueSet-cities.xlsx
+++ b/dev/ValueSet-cities.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T05:11:07+00:00</t>
+    <t>2026-03-16T07:24:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-cities.xlsx
+++ b/dev/ValueSet-cities.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T07:24:26+00:00</t>
+    <t>2026-03-16T20:48:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-cities.xlsx
+++ b/dev/ValueSet-cities.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T20:48:05+00:00</t>
+    <t>2026-03-16T20:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-cities.xlsx
+++ b/dev/ValueSet-cities.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T20:59:47+00:00</t>
+    <t>2026-03-16T21:16:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-cities.xlsx
+++ b/dev/ValueSet-cities.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:16:15+00:00</t>
+    <t>2026-03-16T21:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-cities.xlsx
+++ b/dev/ValueSet-cities.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:44:19+00:00</t>
+    <t>2026-03-16T21:58:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-cities.xlsx
+++ b/dev/ValueSet-cities.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:58:37+00:00</t>
+    <t>2026-03-16T22:06:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-cities.xlsx
+++ b/dev/ValueSet-cities.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T22:06:54+00:00</t>
+    <t>2026-03-16T22:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-cities.xlsx
+++ b/dev/ValueSet-cities.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T22:26:22+00:00</t>
+    <t>2026-03-19T20:53:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-cities.xlsx
+++ b/dev/ValueSet-cities.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T20:53:49+00:00</t>
+    <t>2026-03-19T21:27:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-cities.xlsx
+++ b/dev/ValueSet-cities.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T21:27:42+00:00</t>
+    <t>2026-04-08T04:20:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-cities.xlsx
+++ b/dev/ValueSet-cities.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T04:20:57+00:00</t>
+    <t>2026-04-10T05:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,7 +117,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://doh.gov.ph/fhir/ph-core/CodeSystem/PSGC</t>
+    <t>https://psa.gov.ph/classification/psgc</t>
   </si>
 </sst>
 </file>

--- a/dev/ValueSet-cities.xlsx
+++ b/dev/ValueSet-cities.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:32:03+00:00</t>
+    <t>2026-04-10T05:44:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-cities.xlsx
+++ b/dev/ValueSet-cities.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:44:36+00:00</t>
+    <t>2026-05-26T03:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -109,6 +109,18 @@
   </si>
   <si>
     <t>City of Las Piñas</t>
+  </si>
+  <si>
+    <t>1380600000</t>
+  </si>
+  <si>
+    <t>City of Manila</t>
+  </si>
+  <si>
+    <t>0133070000</t>
+  </si>
+  <si>
+    <t>Bauang</t>
   </si>
   <si>
     <t/>
@@ -381,7 +393,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -417,15 +429,31 @@
         <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/dev/ValueSet-cities.xlsx
+++ b/dev/ValueSet-cities.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T03:51:01+00:00</t>
+    <t>2026-05-26T04:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-cities.xlsx
+++ b/dev/ValueSet-cities.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T04:00:40+00:00</t>
+    <t>2026-05-26T04:36:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
